--- a/data/Nomes-comadres-2026.xlsx
+++ b/data/Nomes-comadres-2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BKP PARTICAO PERDIDA F\CATÁLOGOS LR 4 EM TRABALHO\CONSULTORIAS\MATIAS ENCADERNAÇOES\FERRAMENTAS\GERADOR CERTIFICADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BKP PARTICAO PERDIDA F\CATÁLOGOS LR 4 EM TRABALHO\CONSULTORIAS\MATIAS ENCADERNAÇOES\FERRAMENTAS\GERADOR CERTIFICADOS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Nome</t>
   </si>
@@ -132,6 +132,18 @@
   </si>
   <si>
     <t>123.456.789-01</t>
+  </si>
+  <si>
+    <t>Ana Júlia</t>
+  </si>
+  <si>
+    <t>27 99926-9620</t>
+  </si>
+  <si>
+    <t>Carlos Magno Kill</t>
+  </si>
+  <si>
+    <t>27 99608-9763</t>
   </si>
 </sst>
 </file>
@@ -449,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
@@ -589,6 +601,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
